--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487409_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487409_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1608</v>
+        <v>4.8801</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7135</v>
+        <v>2.0576</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8743</v>
+        <v>2.8226</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5359</v>
+        <v>2.3365</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7213</v>
+        <v>-0.1192</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8146</v>
+        <v>2.4557</v>
       </c>
       <c r="J2" t="n">
-        <v>2.008</v>
+        <v>1.1627</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2401</v>
+        <v>-0.7368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7679</v>
+        <v>1.8995</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5279</v>
+        <v>1.1738</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4812</v>
+        <v>0.6177</v>
       </c>
       <c r="O2" t="n">
-        <v>2.0467</v>
+        <v>0.5562</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7419</v>
+        <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0362</v>
+        <v>-1.1454</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4317</v>
+        <v>-0.5234</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3955</v>
+        <v>-0.6219</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9988</v>
+        <v>2.318</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.9988</v>
+        <v>2.5934</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0847</v>
+        <v>3.4929</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5294</v>
+        <v>-2.0842</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5552</v>
+        <v>5.5771</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3365</v>
+        <v>2.567</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1192</v>
+        <v>4.3301</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4557</v>
+        <v>-1.7631</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1627</v>
+        <v>0.2163</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7368</v>
+        <v>2.824</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8995</v>
+        <v>-2.6077</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1738</v>
+        <v>2.3508</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6177</v>
+        <v>1.5061</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5562</v>
+        <v>0.8446</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3709</v>
+        <v>2.3502</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R3" t="n">
-        <v>2.546</v>
+        <v>4.5045</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9408</v>
+        <v>-2.308</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0516</v>
+        <v>-0.9722</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8893</v>
+        <v>-1.3358</v>
       </c>
       <c r="V3" t="n">
-        <v>2.318</v>
+        <v>0.8837</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5934</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2754</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8878</v>
+        <v>3.06</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8764</v>
+        <v>-1.4134</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7642</v>
+        <v>4.4733</v>
       </c>
       <c r="G4" t="n">
-        <v>2.567</v>
+        <v>4.5359</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3301</v>
+        <v>1.7213</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7631</v>
+        <v>2.8146</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2163</v>
+        <v>2.008</v>
       </c>
       <c r="K4" t="n">
-        <v>2.824</v>
+        <v>1.2401</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6077</v>
+        <v>0.7679</v>
       </c>
       <c r="M4" t="n">
-        <v>2.3508</v>
+        <v>2.5279</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5061</v>
+        <v>0.4812</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8446</v>
+        <v>2.0467</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3502</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R4" t="n">
-        <v>4.5045</v>
+        <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.9131</v>
+        <v>-1.0647</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7644</v>
+        <v>-0.2682</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1487</v>
+        <v>-0.7965</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8837</v>
+        <v>-0.9988</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8260999999999999</v>
+        <v>-0.9988</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7378</v>
+        <v>1.2634</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6566</v>
+        <v>1.102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1614</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0901</v>
@@ -844,13 +844,13 @@
         <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2677</v>
+        <v>-0.7421</v>
       </c>
       <c r="T5" t="n">
-        <v>0.414</v>
+        <v>-0.1406</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6817</v>
+        <v>-0.6015</v>
       </c>
       <c r="V5" t="n">
         <v>0.3329</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2269</v>
+        <v>0.4669</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8685</v>
+        <v>-0.1598</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0954</v>
+        <v>0.6267</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3831</v>
+        <v>1.9055</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0221</v>
+        <v>1.0412</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4052</v>
+        <v>0.8643</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2823</v>
+        <v>1.542</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.5044</v>
+        <v>0.2891</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2221</v>
+        <v>1.2529</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6654</v>
+        <v>0.3634</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4822</v>
+        <v>0.752</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1832</v>
+        <v>-0.3886</v>
       </c>
       <c r="P6" t="n">
-        <v>2.546</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9349</v>
+        <v>-1.5756</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.607</v>
+        <v>-0.627</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3279</v>
+        <v>-0.9487</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7673</v>
+        <v>0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.9839</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BARRIOS UREÑA</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1958</v>
+        <v>0.3876</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1958</v>
+        <v>1.2825</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1364</v>
+        <v>1.3831</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-2.0221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1364</v>
+        <v>3.4052</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1.2823</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-2.5044</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2221</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1364</v>
+        <v>2.6654</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.4822</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1364</v>
+        <v>2.1832</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1958</v>
+        <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1364</v>
+        <v>-1.7743</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.6334</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1364</v>
+        <v>-1.1408</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.9839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>A. BARRIOS UREÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0484</v>
+        <v>0.1958</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3644</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4129</v>
+        <v>0.1958</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9055</v>
+        <v>0.1364</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0412</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8643</v>
+        <v>0.1364</v>
       </c>
       <c r="J8" t="n">
-        <v>1.542</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2891</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2529</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3634</v>
+        <v>0.1364</v>
       </c>
       <c r="N8" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3886</v>
+        <v>0.1364</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9941</v>
+        <v>-0.1364</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8316</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1625</v>
+        <v>-0.1364</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.951</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6686</v>
+        <v>-1.4045</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7176</v>
+        <v>0.6106</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3726</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9494</v>
+        <v>-0.7922</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.593</v>
+        <v>-0.6999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9441</v>
+        <v>-1.842</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8353</v>
+        <v>-4.6824</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8912</v>
+        <v>2.8404</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9487</v>
+        <v>1.4203</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0356</v>
+        <v>-2.1476</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0319</v>
+        <v>-2.5322</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6737</v>
+        <v>0.1871</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6418</v>
+        <v>-2.7193</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1188</v>
+        <v>1.805</v>
       </c>
       <c r="N10" t="n">
-        <v>0.275</v>
+        <v>1.2332</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3938</v>
+        <v>0.5717</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1543</v>
+        <v>-3.917</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>3.7211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8779</v>
+        <v>-1.8601</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7128</v>
+        <v>-0.6664</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1651</v>
+        <v>-1.1938</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.9412</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2073</v>
+        <v>-1.98</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8606</v>
+        <v>-2.6306</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6533</v>
+        <v>0.6506</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4203</v>
+        <v>0.9487</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1476</v>
+        <v>-1.0356</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5322</v>
+        <v>0.0319</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1871</v>
+        <v>0.6737</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7193</v>
+        <v>-0.6418</v>
       </c>
       <c r="M11" t="n">
-        <v>1.805</v>
+        <v>-0.1188</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2332</v>
+        <v>0.275</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5717</v>
+        <v>-0.3938</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.917</v>
+        <v>-2.1543</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7211</v>
+        <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2254</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8446</v>
+        <v>-0.5082</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3809</v>
+        <v>-0.4057</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9412</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.239799999999999</v>
+        <v>9.130799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.0013</v>
+        <v>-10.1103</v>
       </c>
       <c r="F12" t="n">
-        <v>19.2411</v>
+        <v>19.241</v>
       </c>
       <c r="G12" t="n">
         <v>10.5875</v>
@@ -1363,7 +1363,7 @@
         <v>3.437</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1930999999999994</v>
+        <v>0.1931000000000004</v>
       </c>
       <c r="K12" t="n">
         <v>1.6613</v>
@@ -1390,13 +1390,13 @@
         <v>22.5224</v>
       </c>
       <c r="S12" t="n">
-        <v>-13.2035</v>
+        <v>-12.3126</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.322699999999999</v>
+        <v>-4.4317</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.881</v>
+        <v>-7.881000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>2.0426</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2929</v>
+        <v>2.5141</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0775</v>
+        <v>-0.1799</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3704</v>
+        <v>2.6939</v>
       </c>
       <c r="G13" t="n">
         <v>-1.197</v>
@@ -1468,13 +1468,13 @@
         <v>2.1543</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9611</v>
+        <v>1.1823</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7463</v>
+        <v>0.644</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2147</v>
+        <v>0.5383</v>
       </c>
       <c r="V13" t="n">
         <v>1.5495</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.717</v>
+        <v>1.6977</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6212</v>
+        <v>-1.7236</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3383</v>
+        <v>3.4212</v>
       </c>
       <c r="G14" t="n">
         <v>-0.618</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4686</v>
+        <v>2.4493</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3627</v>
+        <v>1.2604</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1059</v>
+        <v>1.1889</v>
       </c>
       <c r="V14" t="n">
         <v>1.8249</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0572</v>
+        <v>0.8904</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6869</v>
+        <v>-1.4822</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7441</v>
+        <v>2.3727</v>
       </c>
       <c r="G15" t="n">
         <v>1.873</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0632</v>
+        <v>2.8964</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2151</v>
+        <v>1.4198</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8481</v>
+        <v>1.4767</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9412</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.672</v>
+        <v>0.2046</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.336</v>
+        <v>-0.643</v>
       </c>
       <c r="F16" t="n">
-        <v>1.008</v>
+        <v>0.8476</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7285</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8129</v>
+        <v>0.3455</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3258</v>
+        <v>0.0188</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4871</v>
+        <v>0.3267</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.303</v>
+        <v>0.1961</v>
       </c>
       <c r="E17" t="n">
         <v>-0.9584</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2614</v>
+        <v>1.1545</v>
       </c>
       <c r="G17" t="n">
         <v>0.6691</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0268</v>
+        <v>0.9198</v>
       </c>
       <c r="T17" t="n">
         <v>0.6163999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4104</v>
+        <v>0.3035</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2178</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. FRAGA CANTELAR</t>
+          <t>F. CORNALIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6309</v>
+        <v>-0.2211</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7806</v>
+        <v>-0.6354</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1497</v>
+        <v>0.4143</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4795</v>
+        <v>0.2213</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6159</v>
+        <v>0.1912</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1364</v>
+        <v>0.03</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3441</v>
+        <v>0.215</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3441</v>
+        <v>0.3266</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.1116</v>
       </c>
       <c r="M18" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="N18" t="n">
         <v>-0.1354</v>
       </c>
-      <c r="N18" t="n">
-        <v>-0.2719</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.1364</v>
+        <v>0.1416</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8486</v>
+        <v>0.3042</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5634</v>
+        <v>0.1288</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2851</v>
+        <v>0.1754</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. CORNALIS</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6378</v>
+        <v>-0.6167</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9424</v>
+        <v>-1.4362</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3046</v>
+        <v>0.8196</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2213</v>
+        <v>-0.9147</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1912</v>
+        <v>-1.2936</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03</v>
+        <v>0.3789</v>
       </c>
       <c r="J19" t="n">
-        <v>0.215</v>
+        <v>-0.3095</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3266</v>
+        <v>-0.9562</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1116</v>
+        <v>0.6466</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0062</v>
+        <v>-0.6052</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1354</v>
+        <v>-0.3375</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1416</v>
+        <v>-0.2677</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1125</v>
+        <v>0.4732</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1782</v>
+        <v>0.2235</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.2497</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5507</v>
+        <v>0.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>B. FRAGA CANTELAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9771</v>
+        <v>-1.0448</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7432</v>
+        <v>-1.0876</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7661</v>
+        <v>0.0428</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9147</v>
+        <v>-1.4795</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2936</v>
+        <v>-1.6159</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3789</v>
+        <v>0.1364</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3095</v>
+        <v>-1.3441</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9562</v>
+        <v>-1.3441</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6466</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6052</v>
+        <v>-0.1354</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3375</v>
+        <v>-0.2719</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2677</v>
+        <v>0.1364</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1127</v>
+        <v>0.4346</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0835</v>
+        <v>0.2564</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1962</v>
+        <v>0.1782</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.992</v>
+        <v>-1.0851</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6425</v>
+        <v>-0.9495</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3495</v>
+        <v>-0.1357</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7283</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8954</v>
+        <v>0.8022</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8234</v>
+        <v>0.5164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.2858</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5507</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3456</v>
+        <v>-2.7412</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9163</v>
+        <v>-4.1537</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5706</v>
+        <v>1.4126</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1456</v>
+        <v>-2.9775</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5438</v>
+        <v>-1.2593</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6018</v>
+        <v>-1.7182</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3653</v>
+        <v>-3.2639</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4803</v>
+        <v>-1.2624</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.885</v>
+        <v>-2.0015</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2197</v>
+        <v>0.2864</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0635</v>
+        <v>0.0031</v>
       </c>
       <c r="O22" t="n">
         <v>0.2833</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7626</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1336</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5626</v>
+        <v>1.4909</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3661</v>
+        <v>1.0686</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1966</v>
+        <v>0.4223</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7691</v>
+        <v>-2.9947</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0747</v>
+        <v>-3.9396</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3056</v>
+        <v>0.9449</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9775</v>
+        <v>-3.1456</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2593</v>
+        <v>-1.5438</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7182</v>
+        <v>-1.6018</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2639</v>
+        <v>-3.3653</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2624</v>
+        <v>-1.4803</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0015</v>
+        <v>-1.885</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2864</v>
+        <v>0.2197</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0031</v>
+        <v>-0.0635</v>
       </c>
       <c r="O23" t="n">
         <v>0.2833</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9792</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-3.1336</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>0.463</v>
+        <v>1.9135</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1476</v>
+        <v>1.3427</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3154</v>
+        <v>0.5708</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9294</v>
+        <v>-4.3569</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4613</v>
+        <v>-2.052</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4681</v>
+        <v>-2.3049</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5618</v>
@@ -2326,13 +2326,13 @@
         <v>0.9792</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1013</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0241</v>
+        <v>0.3852</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1255</v>
+        <v>0.2886</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4896</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.239799999999999</v>
+        <v>-7.5576</v>
       </c>
       <c r="E25" t="n">
-        <v>-19.241</v>
+        <v>-19.2411</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0012</v>
+        <v>11.6835</v>
       </c>
       <c r="G25" t="n">
         <v>-10.5875</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.150399999999999</v>
+        <v>-7.1504</v>
       </c>
       <c r="I25" t="n">
         <v>-3.4373</v>
@@ -2380,7 +2380,7 @@
         <v>-10.3945</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.4892</v>
+        <v>-5.489199999999999</v>
       </c>
       <c r="L25" t="n">
         <v>-4.9053</v>
@@ -2404,13 +2404,13 @@
         <v>13.7091</v>
       </c>
       <c r="S25" t="n">
-        <v>13.2037</v>
+        <v>13.8858</v>
       </c>
       <c r="T25" t="n">
-        <v>7.881</v>
+        <v>7.880999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>5.3227</v>
+        <v>6.0049</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0427</v>
